--- a/data/trans_dic/P56$privada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,95</t>
+          <t>0,0; 63,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,56</t>
+          <t>0,0; 41,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 90,86</t>
+          <t>0,0; 79,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,47</t>
+          <t>0,0; 71,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,77</t>
+          <t>0,0; 59,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 22,52</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,86</t>
+          <t>0,0; 64,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,46</t>
+          <t>0,0; 78,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,33</t>
+          <t>0,0; 43,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,2</t>
+          <t>0,0; 39,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,39</t>
+          <t>0,0; 62,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,33</t>
+          <t>0,0; 49,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 29,52</t>
+          <t>2,87; 30,15</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,34</t>
+          <t>0,0; 56,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 61,48</t>
+          <t>8,47; 63,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 38,14</t>
+          <t>6,86; 40,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 78,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,7</t>
+          <t>0,0; 71,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 34,57</t>
+          <t>8,24; 33,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,67</t>
+          <t>0,0; 41,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,93</t>
+          <t>0,0; 23,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 57,38</t>
+          <t>12,46; 59,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 29,96</t>
+          <t>10,38; 30,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 27,32</t>
+          <t>2,92; 27,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 20,51</t>
+          <t>2,37; 19,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,08</t>
+          <t>0,0; 21,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 24,17</t>
+          <t>7,42; 22,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,67</t>
+          <t>0,0; 24,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 47,93</t>
+          <t>5,48; 49,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 25,9</t>
+          <t>7,33; 26,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 21,62</t>
+          <t>2,26; 21,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 18,45</t>
+          <t>1,81; 15,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 28,09</t>
+          <t>5,68; 28,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 21,04</t>
+          <t>9,08; 21,19</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,42</t>
+          <t>0,0; 34,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 30,44</t>
+          <t>3,21; 31,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 41,6</t>
+          <t>7,76; 37,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 49,68</t>
+          <t>6,16; 46,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,18</t>
+          <t>0,0; 9,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>0,0; 23,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,2; 23,91</t>
+          <t>12,28; 23,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 32,32</t>
+          <t>4,04; 30,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,87</t>
+          <t>1,25; 11,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 18,82</t>
+          <t>3,86; 19,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,37; 24,13</t>
+          <t>12,48; 23,35</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 16,05</t>
+          <t>1,66; 15,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,46; 31,25</t>
+          <t>13,84; 31,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 25,34</t>
+          <t>8,72; 26,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,27; 28,39</t>
+          <t>16,44; 28,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 16,05</t>
+          <t>1,66; 15,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,46; 31,25</t>
+          <t>13,84; 31,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 25,34</t>
+          <t>8,72; 26,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,87; 27,57</t>
+          <t>16,48; 27,56</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 16,46</t>
+          <t>1,77; 16,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 17,28</t>
+          <t>3,93; 18,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,35; 22,84</t>
+          <t>7,05; 22,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,61; 21,46</t>
+          <t>10,39; 21,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 19,65</t>
+          <t>5,63; 19,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,88</t>
+          <t>9,46; 19,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,57; 21,92</t>
+          <t>9,91; 22,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,1; 22,36</t>
+          <t>14,7; 22,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,98</t>
+          <t>6,11; 16,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 17,87</t>
+          <t>8,79; 17,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,0; 20,59</t>
+          <t>10,48; 20,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 20,67</t>
+          <t>14,65; 20,58</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4275</t>
+          <t>0; 4120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2836</t>
+          <t>0; 2379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>0; 3904</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1351</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5273</t>
+          <t>0; 5354</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6452</t>
+          <t>0; 6762</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2470</t>
+          <t>0; 2603</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5154</t>
+          <t>0; 4227</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3856</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4054</t>
+          <t>0; 3793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2367</t>
+          <t>0; 3192</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6051</t>
+          <t>0; 6160</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4428</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>497; 4977</t>
+          <t>484; 5084</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1393</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4139</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>899; 6412</t>
+          <t>884; 6580</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>942; 5230</t>
+          <t>941; 5488</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4473</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1797</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6084</t>
+          <t>0; 5172</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1446; 6235</t>
+          <t>1487; 6017</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4465</t>
+          <t>0; 4391</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6329</t>
+          <t>0; 4065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1899; 10155</t>
+          <t>2206; 10463</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3197; 9511</t>
+          <t>3296; 9619</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>908; 8049</t>
+          <t>861; 8049</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033; 8720</t>
+          <t>1006; 8389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5691</t>
+          <t>0; 5364</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3678; 12218</t>
+          <t>3750; 11299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4493</t>
+          <t>0; 4497</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1235; 10476</t>
+          <t>1199; 10751</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2099; 7301</t>
+          <t>2067; 7351</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>853; 7960</t>
+          <t>832; 8012</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1106; 11204</t>
+          <t>1102; 9697</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2684; 13066</t>
+          <t>2644; 13453</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7199; 16567</t>
+          <t>7148; 16685</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1607</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5700</t>
+          <t>0; 6247</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>821; 7814</t>
+          <t>824; 7981</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1585; 7550</t>
+          <t>1408; 6715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1050; 8575</t>
+          <t>1064; 8051</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7307</t>
+          <t>0; 6391</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7987</t>
+          <t>0; 8255</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10108; 19809</t>
+          <t>10172; 19601</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1078; 8890</t>
+          <t>1110; 8434</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1104; 10742</t>
+          <t>1044; 9619</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2177; 11564</t>
+          <t>2374; 12085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13507; 24373</t>
+          <t>12604; 23584</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1019; 9617</t>
+          <t>993; 9161</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13948; 32383</t>
+          <t>14342; 32363</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7379; 24403</t>
+          <t>8395; 25074</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16796; 29305</t>
+          <t>16967; 29089</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1019; 9617</t>
+          <t>993; 9161</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13948; 32383</t>
+          <t>14342; 32363</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7379; 24403</t>
+          <t>8395; 25074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16717; 29046</t>
+          <t>17368; 29037</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>858; 7949</t>
+          <t>854; 7968</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3142; 13566</t>
+          <t>3089; 14249</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5299; 16468</t>
+          <t>5085; 16395</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10507; 21249</t>
+          <t>10291; 21328</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5480; 18381</t>
+          <t>5267; 18327</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19359; 40617</t>
+          <t>19327; 40311</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16319; 37390</t>
+          <t>16901; 38803</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>37177; 55045</t>
+          <t>36202; 54339</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8182; 22663</t>
+          <t>8667; 23499</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26593; 50525</t>
+          <t>24844; 48288</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24267; 49966</t>
+          <t>25444; 49369</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>50744; 71349</t>
+          <t>50582; 71061</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$privada-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,54</t>
+          <t>0,0; 65,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,57</t>
+          <t>0,0; 43,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,98</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,55</t>
+          <t>0,0; 83,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,49</t>
+          <t>0,0; 54,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,52</t>
+          <t>0,0; 19,88</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,51</t>
+          <t>0,0; 78,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,34</t>
+          <t>0,0; 41,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,37</t>
+          <t>0,0; 27,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,5</t>
+          <t>0,0; 62,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,11</t>
+          <t>0,0; 47,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 30,15</t>
+          <t>2,51; 23,42</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -1002,22 +1002,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,88</t>
+          <t>0,0; 56,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 63,09</t>
+          <t>8,65; 60,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 40,02</t>
+          <t>6,62; 40,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,46</t>
+          <t>0,0; 76,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,16</t>
+          <t>0,0; 84,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 33,36</t>
+          <t>7,16; 31,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,97</t>
+          <t>0,0; 42,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,08</t>
+          <t>0,0; 28,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,46; 59,12</t>
+          <t>13,06; 57,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,38; 30,3</t>
+          <t>9,59; 29,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 27,33</t>
+          <t>3,03; 28,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 19,73</t>
+          <t>2,32; 19,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,75</t>
+          <t>0,0; 21,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 22,36</t>
+          <t>7,24; 25,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,69</t>
+          <t>0,0; 38,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 49,18</t>
+          <t>5,75; 47,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 26,08</t>
+          <t>7,6; 25,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 21,77</t>
+          <t>2,49; 22,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,97</t>
+          <t>1,96; 17,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 28,92</t>
+          <t>6,03; 26,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 21,19</t>
+          <t>9,03; 21,66</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -1282,64 +1282,64 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,43</t>
+          <t>0,0; 29,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 31,09</t>
+          <t>3,18; 29,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 37,0</t>
+          <t>8,66; 38,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 46,64</t>
+          <t>6,16; 46,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,78</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,08</t>
+          <t>0,0; 21,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,28; 23,66</t>
+          <t>12,27; 23,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 30,66</t>
+          <t>3,93; 32,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,52</t>
+          <t>1,26; 11,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 19,67</t>
+          <t>3,45; 19,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,48; 23,35</t>
+          <t>13,45; 24,43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,29</t>
+          <t>1,63; 14,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,84; 31,24</t>
+          <t>13,95; 31,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,72; 26,04</t>
+          <t>8,37; 26,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,44; 28,18</t>
+          <t>16,24; 29,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,29</t>
+          <t>1,63; 14,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,84; 31,24</t>
+          <t>13,95; 31,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,72; 26,04</t>
+          <t>8,37; 26,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,48; 27,56</t>
+          <t>15,97; 28,21</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,5</t>
+          <t>1,84; 16,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 18,15</t>
+          <t>4,05; 18,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 22,74</t>
+          <t>7,12; 22,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 21,54</t>
+          <t>10,47; 22,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 19,59</t>
+          <t>5,61; 20,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 19,73</t>
+          <t>9,26; 19,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,91; 22,75</t>
+          <t>10,59; 23,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 22,07</t>
+          <t>15,19; 22,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,57</t>
+          <t>5,55; 16,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 17,08</t>
+          <t>8,9; 17,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 20,34</t>
+          <t>10,55; 20,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 20,58</t>
+          <t>14,58; 20,62</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>760</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4120</t>
+          <t>0; 4267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2379</t>
+          <t>0; 2553</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3904</t>
+          <t>0; 4882</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5354</t>
+          <t>0; 6282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6762</t>
+          <t>0; 6193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2603</t>
+          <t>0; 2444</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>485</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1775</t>
         </is>
       </c>
     </row>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3809</t>
+          <t>0; 3800</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3793</t>
+          <t>0; 3732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3192</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6160</t>
+          <t>0; 6132</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>484; 5084</t>
+          <t>467; 4362</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6336</t>
         </is>
       </c>
     </row>
@@ -2348,22 +2348,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4035</t>
+          <t>0; 4019</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>884; 6580</t>
+          <t>902; 6338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>941; 5488</t>
+          <t>943; 5750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3509</t>
+          <t>0; 3425</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2373,32 +2373,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5172</t>
+          <t>0; 6153</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1487; 6017</t>
+          <t>1485; 6614</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4391</t>
+          <t>0; 4457</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4065</t>
+          <t>0; 4992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2206; 10463</t>
+          <t>2311; 10161</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3296; 9619</t>
+          <t>3354; 10450</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>12087</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>861; 8049</t>
+          <t>893; 8452</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1006; 8389</t>
+          <t>987; 8378</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5364</t>
+          <t>0; 5366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3750; 11299</t>
+          <t>3956; 13777</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4497</t>
+          <t>0; 6966</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1199; 10751</t>
+          <t>1256; 10457</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2067; 7351</t>
+          <t>2291; 7706</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>832; 8012</t>
+          <t>916; 8101</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1102; 9697</t>
+          <t>1191; 10541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2644; 13453</t>
+          <t>2807; 12442</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7148; 16685</t>
+          <t>7654; 18361</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>15811</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>19659</t>
         </is>
       </c>
     </row>
@@ -2764,64 +2764,64 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6247</t>
+          <t>0; 5437</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>824; 7981</t>
+          <t>816; 7674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1408; 6715</t>
+          <t>1625; 7222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1064; 8051</t>
+          <t>1064; 7955</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6391</t>
+          <t>0; 7085</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 8255</t>
+          <t>0; 7712</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10172; 19601</t>
+          <t>11030; 21088</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1110; 8434</t>
+          <t>1081; 8984</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1044; 9619</t>
+          <t>1048; 9598</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2374; 12085</t>
+          <t>2121; 12121</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12604; 23584</t>
+          <t>14615; 26535</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>24692</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>993; 9161</t>
+          <t>978; 8978</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14342; 32363</t>
+          <t>14453; 32723</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8395; 25074</t>
+          <t>8059; 25225</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16967; 29089</t>
+          <t>18328; 32848</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>993; 9161</t>
+          <t>978; 8978</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14342; 32363</t>
+          <t>14453; 32723</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8395; 25074</t>
+          <t>8059; 25225</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17368; 29037</t>
+          <t>18366; 32448</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>45159</t>
+          <t>49214</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60357</t>
+          <t>65309</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>854; 7968</t>
+          <t>887; 7995</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3089; 14249</t>
+          <t>3182; 14551</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5085; 16395</t>
+          <t>5130; 16313</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10291; 21328</t>
+          <t>10961; 23470</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5267; 18327</t>
+          <t>5244; 19030</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19327; 40311</t>
+          <t>18918; 40821</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16901; 38803</t>
+          <t>18057; 40831</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>36202; 54339</t>
+          <t>40967; 60144</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8667; 23499</t>
+          <t>7866; 23003</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24844; 48288</t>
+          <t>25155; 49827</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25444; 49369</t>
+          <t>25607; 49916</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>50582; 71061</t>
+          <t>54575; 77199</t>
         </is>
       </c>
     </row>
